--- a/reports/evaluation_records.xlsx
+++ b/reports/evaluation_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,6 +1491,189 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DiffuVQA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Medical_VQA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-11-30 18:22:58</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6707547169811321</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.695774647885364</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6581560283678608</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8437865700031735</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8907816781187957</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5577970689422249</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8808963152937282</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6886792452830188</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1060</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-11-30 18:22:58</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DiffuVQA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Medical_VQA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-12-03 21:15:24</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6707547169811321</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.695774647885364</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6581560283678608</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8437865700031735</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8907816781187957</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5577970689422249</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8808963152937282</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6886792452830188</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1060</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-12-03 21:15:24</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DiffuVQA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Medical_VQA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:21:39</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6707547169811321</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.695774647885364</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6581560283678608</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8437865700031735</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8907816781187957</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5577970689422249</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8808963152937282</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8526226878166199</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6886792452830188</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1060</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:21:39</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
